--- a/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/Punktlighet_tog.xlsx
+++ b/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/Punktlighet_tog.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vestfoldfylke-my.sharepoint.com/personal/rasmus_palmqvist_vestfoldfylke_no/Documents/Dokumenter/GitHub/Ny mappe/Vestfold/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="667" documentId="8_{840FB08B-DE99-453E-B629-E89AADE1FD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{944B3435-B6DB-4EDB-831E-C3069AC3F9D1}"/>
+  <xr:revisionPtr revIDLastSave="680" documentId="8_{840FB08B-DE99-453E-B629-E89AADE1FD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F4076B3-678E-4FCF-8725-9A8BEBE73244}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="57840" windowHeight="15720" activeTab="1" xr2:uid="{505C7C03-B5C0-43C5-A197-1F7CDBCB9E10}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{505C7C03-B5C0-43C5-A197-1F7CDBCB9E10}"/>
   </bookViews>
   <sheets>
     <sheet name="Punktlighet" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2135" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2151" uniqueCount="41">
   <si>
     <t>År</t>
   </si>
@@ -261,7 +261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -288,7 +288,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5170,10 +5169,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter>
-    <oddHeader>&amp;R&amp;"Arial"&amp;10&amp;KFF8C00 I N T E R N&amp;1#_x000D_</oddHeader>
-    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Arial"&amp;10&amp;KFF8C00 I N T E R N</oddFooter>
-  </headerFooter>
 </worksheet>
 </file>
 
@@ -29998,7 +29993,7 @@
       <c r="A771" s="4">
         <v>2026</v>
       </c>
-      <c r="B771" s="16" t="s">
+      <c r="B771" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C771" s="9">
@@ -30033,7 +30028,7 @@
       <c r="A772" s="4">
         <v>2026</v>
       </c>
-      <c r="B772" s="16" t="s">
+      <c r="B772" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C772" s="9">
@@ -30068,7 +30063,7 @@
       <c r="A773" s="4">
         <v>2026</v>
       </c>
-      <c r="B773" s="16" t="s">
+      <c r="B773" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C773" s="9">
@@ -30103,7 +30098,7 @@
       <c r="A774" s="4">
         <v>2026</v>
       </c>
-      <c r="B774" s="16" t="s">
+      <c r="B774" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C774" s="9">
@@ -30138,7 +30133,7 @@
       <c r="A775" s="4">
         <v>2026</v>
       </c>
-      <c r="B775" s="16" t="s">
+      <c r="B775" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C775" s="9">
@@ -30171,7 +30166,7 @@
       <c r="A776" s="4">
         <v>2026</v>
       </c>
-      <c r="B776" s="16" t="s">
+      <c r="B776" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C776" s="9">
@@ -30204,7 +30199,7 @@
       <c r="A777" s="4">
         <v>2026</v>
       </c>
-      <c r="B777" s="16" t="s">
+      <c r="B777" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C777" s="9">
@@ -30237,7 +30232,7 @@
       <c r="A778" s="4">
         <v>2026</v>
       </c>
-      <c r="B778" s="16" t="s">
+      <c r="B778" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C778" s="9">
@@ -30270,7 +30265,7 @@
       <c r="A779" s="4">
         <v>2026</v>
       </c>
-      <c r="B779" s="16" t="s">
+      <c r="B779" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C779" s="9">
@@ -30303,7 +30298,7 @@
       <c r="A780" s="4">
         <v>2026</v>
       </c>
-      <c r="B780" s="16" t="s">
+      <c r="B780" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C780" s="9">
@@ -30336,7 +30331,7 @@
       <c r="A781" s="4">
         <v>2026</v>
       </c>
-      <c r="B781" s="16" t="s">
+      <c r="B781" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C781" s="9">
@@ -30369,7 +30364,7 @@
       <c r="A782" s="4">
         <v>2026</v>
       </c>
-      <c r="B782" s="16" t="s">
+      <c r="B782" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C782" s="9">
@@ -30402,7 +30397,7 @@
       <c r="A783" s="4">
         <v>2026</v>
       </c>
-      <c r="B783" s="16" t="s">
+      <c r="B783" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C783" s="9">
@@ -30435,7 +30430,7 @@
       <c r="A784" s="4">
         <v>2026</v>
       </c>
-      <c r="B784" s="16" t="s">
+      <c r="B784" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C784" s="9">
@@ -30468,7 +30463,7 @@
       <c r="A785" s="4">
         <v>2026</v>
       </c>
-      <c r="B785" s="16" t="s">
+      <c r="B785" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C785" s="9">
@@ -30501,7 +30496,7 @@
       <c r="A786" s="4">
         <v>2026</v>
       </c>
-      <c r="B786" s="16" t="s">
+      <c r="B786" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C786" s="9">
@@ -30534,7 +30529,7 @@
       <c r="A787" s="4">
         <v>2026</v>
       </c>
-      <c r="B787" s="16" t="s">
+      <c r="B787" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C787" s="9">
@@ -30568,7 +30563,7 @@
       <c r="A788" s="4">
         <v>2026</v>
       </c>
-      <c r="B788" s="16" t="s">
+      <c r="B788" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C788" s="9">
@@ -30602,7 +30597,7 @@
       <c r="A789" s="4">
         <v>2026</v>
       </c>
-      <c r="B789" s="16" t="s">
+      <c r="B789" s="4" t="s">
         <v>16</v>
       </c>
       <c r="C789" s="9">
@@ -30636,7 +30631,7 @@
       <c r="A790" s="4">
         <v>2026</v>
       </c>
-      <c r="B790" s="16" t="s">
+      <c r="B790" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C790" s="9">
@@ -30670,7 +30665,7 @@
       <c r="A791" s="4">
         <v>2026</v>
       </c>
-      <c r="B791" s="16" t="s">
+      <c r="B791" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C791" s="9">
@@ -30704,7 +30699,7 @@
       <c r="A792" s="4">
         <v>2026</v>
       </c>
-      <c r="B792" s="16" t="s">
+      <c r="B792" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C792" s="9">
@@ -30738,7 +30733,7 @@
       <c r="A793" s="4">
         <v>2026</v>
       </c>
-      <c r="B793" s="16" t="s">
+      <c r="B793" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C793" s="9">
@@ -30772,7 +30767,7 @@
       <c r="A794" s="4">
         <v>2026</v>
       </c>
-      <c r="B794" s="16" t="s">
+      <c r="B794" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C794" s="9">
@@ -30806,7 +30801,7 @@
       <c r="A795" s="4">
         <v>2026</v>
       </c>
-      <c r="B795" s="16" t="s">
+      <c r="B795" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C795" s="9">
@@ -30838,7 +30833,7 @@
       <c r="A796" s="4">
         <v>2026</v>
       </c>
-      <c r="B796" s="16" t="s">
+      <c r="B796" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C796" s="9">
@@ -30870,7 +30865,7 @@
       <c r="A797" s="4">
         <v>2026</v>
       </c>
-      <c r="B797" s="16" t="s">
+      <c r="B797" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C797" s="9">
@@ -30902,7 +30897,7 @@
       <c r="A798" s="4">
         <v>2026</v>
       </c>
-      <c r="B798" s="16" t="s">
+      <c r="B798" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C798" s="9">
@@ -30934,7 +30929,7 @@
       <c r="A799" s="4">
         <v>2026</v>
       </c>
-      <c r="B799" s="16" t="s">
+      <c r="B799" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C799" s="9">
@@ -30966,7 +30961,7 @@
       <c r="A800" s="4">
         <v>2026</v>
       </c>
-      <c r="B800" s="16" t="s">
+      <c r="B800" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C800" s="9">
@@ -30998,7 +30993,7 @@
       <c r="A801" s="4">
         <v>2026</v>
       </c>
-      <c r="B801" s="16" t="s">
+      <c r="B801" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C801" s="9">
@@ -31030,7 +31025,7 @@
       <c r="A802" s="4">
         <v>2026</v>
       </c>
-      <c r="B802" s="16" t="s">
+      <c r="B802" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C802" s="9">
@@ -31062,7 +31057,7 @@
       <c r="A803" s="4">
         <v>2026</v>
       </c>
-      <c r="B803" s="16" t="s">
+      <c r="B803" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C803" s="9">
@@ -31094,7 +31089,7 @@
       <c r="A804" s="4">
         <v>2026</v>
       </c>
-      <c r="B804" s="16" t="s">
+      <c r="B804" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C804" s="9">
@@ -31126,7 +31121,7 @@
       <c r="A805" s="4">
         <v>2026</v>
       </c>
-      <c r="B805" s="16" t="s">
+      <c r="B805" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C805" s="9">
@@ -31158,7 +31153,7 @@
       <c r="A806" s="4">
         <v>2026</v>
       </c>
-      <c r="B806" s="16" t="s">
+      <c r="B806" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C806" s="9">
@@ -31190,7 +31185,7 @@
       <c r="A807" s="4">
         <v>2026</v>
       </c>
-      <c r="B807" s="16" t="s">
+      <c r="B807" s="4" t="s">
         <v>18</v>
       </c>
       <c r="C807" s="9">
@@ -31222,7 +31217,7 @@
       <c r="A808" s="4">
         <v>2026</v>
       </c>
-      <c r="B808" s="16" t="s">
+      <c r="B808" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C808" s="9">
@@ -31254,7 +31249,7 @@
       <c r="A809" s="4">
         <v>2026</v>
       </c>
-      <c r="B809" s="16" t="s">
+      <c r="B809" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C809" s="9">
@@ -31286,7 +31281,7 @@
       <c r="A810" s="4">
         <v>2026</v>
       </c>
-      <c r="B810" s="16" t="s">
+      <c r="B810" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C810" s="9">
@@ -31318,7 +31313,7 @@
       <c r="A811" s="4">
         <v>2026</v>
       </c>
-      <c r="B811" s="16" t="s">
+      <c r="B811" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C811" s="9">
@@ -31350,7 +31345,7 @@
       <c r="A812" s="4">
         <v>2026</v>
       </c>
-      <c r="B812" s="16" t="s">
+      <c r="B812" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C812" s="9">
@@ -31382,7 +31377,7 @@
       <c r="A813" s="4">
         <v>2026</v>
       </c>
-      <c r="B813" s="16" t="s">
+      <c r="B813" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C813" s="9">
@@ -31414,7 +31409,7 @@
       <c r="A814" s="4">
         <v>2026</v>
       </c>
-      <c r="B814" s="16" t="s">
+      <c r="B814" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C814" s="9">
@@ -31446,7 +31441,7 @@
       <c r="A815" s="4">
         <v>2026</v>
       </c>
-      <c r="B815" s="16" t="s">
+      <c r="B815" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C815" s="9">
@@ -31478,7 +31473,7 @@
       <c r="A816" s="4">
         <v>2026</v>
       </c>
-      <c r="B816" s="16" t="s">
+      <c r="B816" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C816" s="9">
@@ -31506,82 +31501,298 @@
       <c r="V816" s="9"/>
       <c r="W816" s="10"/>
     </row>
-    <row r="817" spans="19:23" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A817" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B817" t="s">
+        <v>20</v>
+      </c>
+      <c r="C817" s="9">
+        <v>91.331269349845201</v>
+      </c>
+      <c r="D817" s="9">
+        <v>75.748031496062993</v>
+      </c>
+      <c r="E817" t="s">
+        <v>4</v>
+      </c>
+      <c r="F817" s="10">
+        <v>646</v>
+      </c>
+      <c r="G817" s="10">
+        <v>635</v>
+      </c>
+      <c r="M817" s="9">
+        <v>91.331269349845201</v>
+      </c>
+      <c r="N817" s="9">
+        <v>75.748031496062993</v>
+      </c>
       <c r="S817" s="11"/>
       <c r="V817" s="9"/>
       <c r="W817" s="10"/>
     </row>
-    <row r="818" spans="19:23" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A818" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B818" t="s">
+        <v>20</v>
+      </c>
+      <c r="C818" s="9">
+        <v>85.77981651376146</v>
+      </c>
+      <c r="D818" s="9">
+        <v>69.278996865203752</v>
+      </c>
+      <c r="E818" t="s">
+        <v>5</v>
+      </c>
+      <c r="F818" s="10">
+        <v>654</v>
+      </c>
+      <c r="G818" s="10">
+        <v>640</v>
+      </c>
+      <c r="M818" s="9">
+        <v>85.77981651376146</v>
+      </c>
+      <c r="N818" s="9">
+        <v>69.278996865203752</v>
+      </c>
       <c r="S818" s="11"/>
       <c r="V818" s="9"/>
       <c r="W818" s="10"/>
     </row>
-    <row r="819" spans="19:23" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A819" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B819" t="s">
+        <v>20</v>
+      </c>
+      <c r="C819" s="9">
+        <v>87.38601823708207</v>
+      </c>
+      <c r="D819" s="9">
+        <v>76.131045241809673</v>
+      </c>
+      <c r="E819" t="s">
+        <v>6</v>
+      </c>
+      <c r="F819" s="10">
+        <v>660</v>
+      </c>
+      <c r="G819" s="10">
+        <v>645</v>
+      </c>
+      <c r="M819" s="9">
+        <v>87.38601823708207</v>
+      </c>
+      <c r="N819" s="9">
+        <v>76.131045241809673</v>
+      </c>
       <c r="S819" s="11"/>
       <c r="V819" s="9"/>
       <c r="W819" s="10"/>
     </row>
-    <row r="820" spans="19:23" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A820" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B820" t="s">
+        <v>20</v>
+      </c>
+      <c r="C820" s="9">
+        <v>88.807069219440351</v>
+      </c>
+      <c r="D820" s="9">
+        <v>90</v>
+      </c>
+      <c r="E820" t="s">
+        <v>7</v>
+      </c>
+      <c r="F820" s="10">
+        <v>679</v>
+      </c>
+      <c r="G820" s="10">
+        <v>667</v>
+      </c>
+      <c r="M820" s="9">
+        <v>88.807069219440351</v>
+      </c>
+      <c r="N820" s="9">
+        <v>90</v>
+      </c>
       <c r="S820" s="11"/>
       <c r="V820" s="9"/>
       <c r="W820" s="10"/>
     </row>
-    <row r="821" spans="19:23" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A821" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B821" t="s">
+        <v>20</v>
+      </c>
+      <c r="C821" s="9">
+        <v>85.545722713864308</v>
+      </c>
+      <c r="D821" s="9">
+        <v>73.123123123123122</v>
+      </c>
+      <c r="E821" t="s">
+        <v>8</v>
+      </c>
+      <c r="F821" s="10">
+        <v>679</v>
+      </c>
+      <c r="G821" s="10">
+        <v>668</v>
+      </c>
+      <c r="M821" s="9">
+        <v>85.545722713864308</v>
+      </c>
+      <c r="N821" s="9">
+        <v>73.123123123123122</v>
+      </c>
       <c r="S821" s="11"/>
       <c r="V821" s="9"/>
       <c r="W821" s="10"/>
     </row>
-    <row r="822" spans="19:23" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A822" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B822" t="s">
+        <v>20</v>
+      </c>
+      <c r="C822" s="9">
+        <v>100</v>
+      </c>
+      <c r="D822" s="9">
+        <v>74.212893553223381</v>
+      </c>
+      <c r="E822" t="s">
+        <v>9</v>
+      </c>
+      <c r="F822" s="10">
+        <v>679</v>
+      </c>
+      <c r="G822" s="10">
+        <v>670</v>
+      </c>
+      <c r="M822" s="9">
+        <v>100</v>
+      </c>
+      <c r="N822" s="9">
+        <v>74.212893553223381</v>
+      </c>
       <c r="S822" s="11"/>
       <c r="V822" s="9"/>
       <c r="W822" s="10"/>
     </row>
-    <row r="823" spans="19:23" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A823" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B823" t="s">
+        <v>20</v>
+      </c>
+      <c r="C823" s="9">
+        <v>86.060606060606062</v>
+      </c>
+      <c r="D823" s="9">
+        <v>61.38461538461538</v>
+      </c>
+      <c r="E823" t="s">
+        <v>10</v>
+      </c>
+      <c r="F823" s="10">
+        <v>660</v>
+      </c>
+      <c r="G823" s="10">
+        <v>650</v>
+      </c>
+      <c r="M823" s="9">
+        <v>86.060606060606062</v>
+      </c>
+      <c r="N823" s="9">
+        <v>61.38461538461538</v>
+      </c>
       <c r="S823" s="11"/>
       <c r="V823" s="9"/>
       <c r="W823" s="10"/>
     </row>
-    <row r="824" spans="19:23" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A824" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B824" t="s">
+        <v>20</v>
+      </c>
+      <c r="C824" s="9">
+        <v>84.393939393939405</v>
+      </c>
+      <c r="D824" s="9">
+        <v>63.076923076923073</v>
+      </c>
+      <c r="E824" t="s">
+        <v>11</v>
+      </c>
+      <c r="F824" s="10">
+        <v>660</v>
+      </c>
+      <c r="G824" s="10">
+        <v>650</v>
+      </c>
+      <c r="M824" s="9">
+        <v>84.393939393939405</v>
+      </c>
+      <c r="N824" s="9">
+        <v>63.076923076923073</v>
+      </c>
       <c r="S824" s="11"/>
       <c r="V824" s="9"/>
       <c r="W824" s="10"/>
     </row>
-    <row r="825" spans="19:23" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:23" x14ac:dyDescent="0.25">
       <c r="S825" s="11"/>
       <c r="V825" s="9"/>
       <c r="W825" s="10"/>
     </row>
-    <row r="826" spans="19:23" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:23" x14ac:dyDescent="0.25">
       <c r="S826" s="11"/>
       <c r="V826" s="9"/>
       <c r="W826" s="10"/>
     </row>
-    <row r="827" spans="19:23" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:23" x14ac:dyDescent="0.25">
       <c r="S827" s="11"/>
       <c r="V827" s="9"/>
       <c r="W827" s="10"/>
     </row>
-    <row r="828" spans="19:23" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:23" x14ac:dyDescent="0.25">
       <c r="S828" s="11"/>
       <c r="V828" s="9"/>
       <c r="W828" s="10"/>
     </row>
-    <row r="829" spans="19:23" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:23" x14ac:dyDescent="0.25">
       <c r="S829" s="11"/>
       <c r="V829" s="9"/>
       <c r="W829" s="10"/>
     </row>
-    <row r="830" spans="19:23" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:23" x14ac:dyDescent="0.25">
       <c r="S830" s="11"/>
       <c r="V830" s="9"/>
       <c r="W830" s="10"/>
     </row>
-    <row r="831" spans="19:23" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:23" x14ac:dyDescent="0.25">
       <c r="S831" s="11"/>
       <c r="V831" s="9"/>
       <c r="W831" s="10"/>
     </row>
-    <row r="832" spans="19:23" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:23" x14ac:dyDescent="0.25">
       <c r="S832" s="11"/>
       <c r="V832" s="9"/>
       <c r="W832" s="10"/>
@@ -36349,11 +36560,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A39:A50"/>
-    <mergeCell ref="A51:A62"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="A63:A74"/>
     <mergeCell ref="S2:T2"/>
     <mergeCell ref="A3:A14"/>
     <mergeCell ref="A15:A26"/>
@@ -36364,13 +36570,14 @@
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="M2:N2"/>
+    <mergeCell ref="A39:A50"/>
+    <mergeCell ref="A51:A62"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="A63:A74"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter>
-    <oddHeader>&amp;R&amp;"Arial"&amp;10&amp;KFF8C00 I N T E R N&amp;1#_x000D_</oddHeader>
-    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Arial"&amp;10&amp;KFF8C00 I N T E R N</oddFooter>
-  </headerFooter>
 </worksheet>
 </file>
 
@@ -36384,17 +36591,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="304c15a9-2ddf-417f-8912-8cf6a1609eab">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ec2c31f6-e4da-4ac2-b928-7a50ed07fae6" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101001F0BB1C88B026E498516C75AD9D26285" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5fb15fa5fb8ec6c836b9d7d5a959bb8a">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="304c15a9-2ddf-417f-8912-8cf6a1609eab" xmlns:ns3="ec2c31f6-e4da-4ac2-b928-7a50ed07fae6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9ddd68b27bb9e6f16d84f1577050cb1c" ns2:_="" ns3:_="">
     <xsd:import namespace="304c15a9-2ddf-417f-8912-8cf6a1609eab"/>
@@ -36649,6 +36845,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="304c15a9-2ddf-417f-8912-8cf6a1609eab">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ec2c31f6-e4da-4ac2-b928-7a50ed07fae6" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7B921E6-00DE-4D0E-B400-431DDE188271}">
   <ds:schemaRefs>
@@ -36658,17 +36865,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11171811-4752-42CE-913B-A1196C5C2AA8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="304c15a9-2ddf-417f-8912-8cf6a1609eab"/>
-    <ds:schemaRef ds:uri="ec2c31f6-e4da-4ac2-b928-7a50ed07fae6"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BAB492D-29AE-4FBB-B174-1C81B2D3C817}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -36685,4 +36881,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11171811-4752-42CE-913B-A1196C5C2AA8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="304c15a9-2ddf-417f-8912-8cf6a1609eab"/>
+    <ds:schemaRef ds:uri="ec2c31f6-e4da-4ac2-b928-7a50ed07fae6"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{24007f1f-a397-4c20-bfe2-4e251f78f126}" enabled="1" method="Standard" siteId="{0a8a3b9a-8dcd-4ebc-9305-f971454d49bb}" removed="0"/>
+</clbl:labelList>
 </file>
--- a/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/Punktlighet_tog.xlsx
+++ b/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/Punktlighet_tog.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vestfoldfylke-my.sharepoint.com/personal/rasmus_palmqvist_vestfoldfylke_no/Documents/Dokumenter/GitHub/Ny mappe/Vestfold/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="680" documentId="8_{840FB08B-DE99-453E-B629-E89AADE1FD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F4076B3-678E-4FCF-8725-9A8BEBE73244}"/>
+  <xr:revisionPtr revIDLastSave="721" documentId="8_{840FB08B-DE99-453E-B629-E89AADE1FD89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFDB0E81-7091-4A45-ABEA-59239D442606}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{505C7C03-B5C0-43C5-A197-1F7CDBCB9E10}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2151" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2167" uniqueCount="41">
   <si>
     <t>År</t>
   </si>
@@ -261,7 +261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -288,6 +288,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -31758,201 +31759,449 @@
       <c r="W824" s="10"/>
     </row>
     <row r="825" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A825" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B825" t="s">
+        <v>21</v>
+      </c>
+      <c r="C825" s="9">
+        <v>91.549295774647888</v>
+      </c>
+      <c r="D825" s="9">
+        <v>82.725832012678296</v>
+      </c>
+      <c r="E825" t="s">
+        <v>4</v>
+      </c>
+      <c r="F825" s="10">
+        <v>639</v>
+      </c>
+      <c r="G825" s="10">
+        <v>631</v>
+      </c>
+      <c r="M825" s="9">
+        <v>91.549295774647888</v>
+      </c>
+      <c r="N825" s="9">
+        <v>82.725832012678296</v>
+      </c>
       <c r="S825" s="11"/>
       <c r="V825" s="9"/>
       <c r="W825" s="10"/>
     </row>
     <row r="826" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A826" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B826" t="s">
+        <v>21</v>
+      </c>
+      <c r="C826" s="9">
+        <v>86.739469578783158</v>
+      </c>
+      <c r="D826" s="9">
+        <v>72.327044025157235</v>
+      </c>
+      <c r="E826" t="s">
+        <v>5</v>
+      </c>
+      <c r="F826" s="10">
+        <v>641</v>
+      </c>
+      <c r="G826" s="10">
+        <v>637</v>
+      </c>
+      <c r="M826" s="9">
+        <v>86.739469578783158</v>
+      </c>
+      <c r="N826" s="9">
+        <v>72.327044025157235</v>
+      </c>
       <c r="S826" s="11"/>
       <c r="V826" s="9"/>
       <c r="W826" s="10"/>
     </row>
     <row r="827" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A827" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B827" t="s">
+        <v>21</v>
+      </c>
+      <c r="C827" s="9">
+        <v>87.869362363919137</v>
+      </c>
+      <c r="D827" s="9">
+        <v>80.690737833594966</v>
+      </c>
+      <c r="E827" t="s">
+        <v>6</v>
+      </c>
+      <c r="F827" s="10">
+        <v>643</v>
+      </c>
+      <c r="G827" s="10">
+        <v>646</v>
+      </c>
+      <c r="M827" s="9">
+        <v>87.869362363919137</v>
+      </c>
+      <c r="N827" s="9">
+        <v>80.690737833594966</v>
+      </c>
       <c r="S827" s="11"/>
       <c r="V827" s="9"/>
       <c r="W827" s="10"/>
     </row>
     <row r="828" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A828" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B828" t="s">
+        <v>21</v>
+      </c>
+      <c r="C828" s="9">
+        <v>88.536953242835594</v>
+      </c>
+      <c r="D828" s="9">
+        <v>94.736842105263165</v>
+      </c>
+      <c r="E828" t="s">
+        <v>7</v>
+      </c>
+      <c r="F828" s="10">
+        <v>663</v>
+      </c>
+      <c r="G828" s="10">
+        <v>669</v>
+      </c>
+      <c r="M828" s="9">
+        <v>88.536953242835594</v>
+      </c>
+      <c r="N828" s="9">
+        <v>94.736842105263165</v>
+      </c>
       <c r="S828" s="11"/>
       <c r="V828" s="9"/>
       <c r="W828" s="10"/>
     </row>
     <row r="829" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A829" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B829" t="s">
+        <v>21</v>
+      </c>
+      <c r="C829" s="9">
+        <v>86.425339366515843</v>
+      </c>
+      <c r="D829" s="9">
+        <v>77.877428998505223</v>
+      </c>
+      <c r="E829" t="s">
+        <v>8</v>
+      </c>
+      <c r="F829" s="10">
+        <v>664</v>
+      </c>
+      <c r="G829" s="10">
+        <v>670</v>
+      </c>
+      <c r="M829" s="9">
+        <v>86.425339366515843</v>
+      </c>
+      <c r="N829" s="9">
+        <v>77.877428998505223</v>
+      </c>
       <c r="S829" s="11"/>
       <c r="V829" s="9"/>
       <c r="W829" s="10"/>
     </row>
     <row r="830" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A830" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B830" t="s">
+        <v>21</v>
+      </c>
+      <c r="C830" s="9">
+        <v>94.736842105263165</v>
+      </c>
+      <c r="D830" s="9">
+        <v>80.547112462006083</v>
+      </c>
+      <c r="E830" t="s">
+        <v>9</v>
+      </c>
+      <c r="F830" s="10">
+        <v>663</v>
+      </c>
+      <c r="G830" s="10">
+        <v>671</v>
+      </c>
+      <c r="M830" s="9">
+        <v>94.736842105263165</v>
+      </c>
+      <c r="N830" s="9">
+        <v>80.547112462006083</v>
+      </c>
       <c r="S830" s="11"/>
       <c r="V830" s="9"/>
       <c r="W830" s="10"/>
     </row>
     <row r="831" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A831" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B831" t="s">
+        <v>21</v>
+      </c>
+      <c r="C831" s="9">
+        <v>88.975155279503099</v>
+      </c>
+      <c r="D831" s="9">
+        <v>74.347158218125969</v>
+      </c>
+      <c r="E831" t="s">
+        <v>10</v>
+      </c>
+      <c r="F831" s="10">
+        <v>644</v>
+      </c>
+      <c r="G831" s="10">
+        <v>651</v>
+      </c>
+      <c r="M831" s="9">
+        <v>88.975155279503099</v>
+      </c>
+      <c r="N831" s="9">
+        <v>74.347158218125969</v>
+      </c>
       <c r="S831" s="11"/>
       <c r="V831" s="9"/>
       <c r="W831" s="10"/>
     </row>
     <row r="832" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A832" s="16">
+        <v>2026</v>
+      </c>
+      <c r="B832" t="s">
+        <v>21</v>
+      </c>
+      <c r="C832" s="9">
+        <v>84.782608695652172</v>
+      </c>
+      <c r="D832" s="9">
+        <v>78.153846153846146</v>
+      </c>
+      <c r="E832" t="s">
+        <v>11</v>
+      </c>
+      <c r="F832" s="10">
+        <v>644</v>
+      </c>
+      <c r="G832" s="10">
+        <v>651</v>
+      </c>
+      <c r="M832" s="9">
+        <v>84.782608695652172</v>
+      </c>
+      <c r="N832" s="9">
+        <v>78.153846153846146</v>
+      </c>
       <c r="S832" s="11"/>
       <c r="V832" s="9"/>
       <c r="W832" s="10"/>
     </row>
-    <row r="833" spans="19:23" x14ac:dyDescent="0.25">
+    <row r="833" spans="17:23" x14ac:dyDescent="0.25">
       <c r="S833" s="11"/>
       <c r="V833" s="9"/>
       <c r="W833" s="10"/>
     </row>
-    <row r="834" spans="19:23" x14ac:dyDescent="0.25">
+    <row r="834" spans="17:23" x14ac:dyDescent="0.25">
       <c r="S834" s="11"/>
       <c r="V834" s="9"/>
       <c r="W834" s="10"/>
     </row>
-    <row r="835" spans="19:23" x14ac:dyDescent="0.25">
+    <row r="835" spans="17:23" x14ac:dyDescent="0.25">
       <c r="S835" s="11"/>
       <c r="V835" s="9"/>
       <c r="W835" s="10"/>
     </row>
-    <row r="836" spans="19:23" x14ac:dyDescent="0.25">
+    <row r="836" spans="17:23" x14ac:dyDescent="0.25">
       <c r="S836" s="11"/>
       <c r="V836" s="9"/>
       <c r="W836" s="10"/>
     </row>
-    <row r="837" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S837" s="11"/>
+    <row r="837" spans="17:23" x14ac:dyDescent="0.25">
+      <c r="Q837" s="11"/>
+      <c r="T837" s="9"/>
+      <c r="U837" s="10"/>
       <c r="V837" s="9"/>
       <c r="W837" s="10"/>
     </row>
-    <row r="838" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S838" s="11"/>
+    <row r="838" spans="17:23" x14ac:dyDescent="0.25">
+      <c r="Q838" s="11"/>
+      <c r="T838" s="9"/>
+      <c r="U838" s="10"/>
       <c r="V838" s="9"/>
       <c r="W838" s="10"/>
     </row>
-    <row r="839" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S839" s="11"/>
+    <row r="839" spans="17:23" x14ac:dyDescent="0.25">
+      <c r="Q839" s="11"/>
+      <c r="T839" s="9"/>
+      <c r="U839" s="10"/>
       <c r="V839" s="9"/>
       <c r="W839" s="10"/>
     </row>
-    <row r="840" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S840" s="11"/>
+    <row r="840" spans="17:23" x14ac:dyDescent="0.25">
+      <c r="Q840" s="11"/>
+      <c r="T840" s="9"/>
+      <c r="U840" s="10"/>
       <c r="V840" s="9"/>
       <c r="W840" s="10"/>
     </row>
-    <row r="841" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S841" s="11"/>
+    <row r="841" spans="17:23" x14ac:dyDescent="0.25">
+      <c r="Q841" s="11"/>
+      <c r="T841" s="9"/>
+      <c r="U841" s="10"/>
       <c r="V841" s="9"/>
       <c r="W841" s="10"/>
     </row>
-    <row r="842" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S842" s="11"/>
+    <row r="842" spans="17:23" x14ac:dyDescent="0.25">
+      <c r="Q842" s="11"/>
+      <c r="T842" s="9"/>
+      <c r="U842" s="10"/>
       <c r="V842" s="9"/>
       <c r="W842" s="10"/>
     </row>
-    <row r="843" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S843" s="11"/>
+    <row r="843" spans="17:23" x14ac:dyDescent="0.25">
+      <c r="Q843" s="11"/>
+      <c r="T843" s="9"/>
+      <c r="U843" s="10"/>
       <c r="V843" s="9"/>
       <c r="W843" s="10"/>
     </row>
-    <row r="844" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S844" s="11"/>
+    <row r="844" spans="17:23" x14ac:dyDescent="0.25">
+      <c r="Q844" s="11"/>
+      <c r="T844" s="9"/>
+      <c r="U844" s="10"/>
       <c r="V844" s="9"/>
       <c r="W844" s="10"/>
     </row>
-    <row r="845" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S845" s="11"/>
+    <row r="845" spans="17:23" x14ac:dyDescent="0.25">
+      <c r="Q845" s="11"/>
+      <c r="T845" s="9"/>
+      <c r="U845" s="10"/>
       <c r="V845" s="9"/>
       <c r="W845" s="10"/>
     </row>
-    <row r="846" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S846" s="11"/>
+    <row r="846" spans="17:23" x14ac:dyDescent="0.25">
+      <c r="Q846" s="11"/>
+      <c r="T846" s="9"/>
+      <c r="U846" s="10"/>
       <c r="V846" s="9"/>
       <c r="W846" s="10"/>
     </row>
-    <row r="847" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S847" s="11"/>
+    <row r="847" spans="17:23" x14ac:dyDescent="0.25">
+      <c r="Q847" s="11"/>
+      <c r="T847" s="9"/>
+      <c r="U847" s="10"/>
       <c r="V847" s="9"/>
       <c r="W847" s="10"/>
     </row>
-    <row r="848" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S848" s="11"/>
+    <row r="848" spans="17:23" x14ac:dyDescent="0.25">
+      <c r="Q848" s="11"/>
+      <c r="T848" s="9"/>
+      <c r="U848" s="10"/>
       <c r="V848" s="9"/>
       <c r="W848" s="10"/>
     </row>
-    <row r="849" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S849" s="11"/>
+    <row r="849" spans="17:23" x14ac:dyDescent="0.25">
+      <c r="Q849" s="11"/>
+      <c r="T849" s="9"/>
+      <c r="U849" s="10"/>
       <c r="V849" s="9"/>
       <c r="W849" s="10"/>
     </row>
-    <row r="850" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S850" s="11"/>
+    <row r="850" spans="17:23" x14ac:dyDescent="0.25">
+      <c r="Q850" s="11"/>
+      <c r="T850" s="9"/>
+      <c r="U850" s="10"/>
       <c r="V850" s="9"/>
       <c r="W850" s="10"/>
     </row>
-    <row r="851" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S851" s="11"/>
+    <row r="851" spans="17:23" x14ac:dyDescent="0.25">
+      <c r="Q851" s="11"/>
+      <c r="T851" s="9"/>
+      <c r="U851" s="10"/>
       <c r="V851" s="9"/>
       <c r="W851" s="10"/>
     </row>
-    <row r="852" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S852" s="11"/>
+    <row r="852" spans="17:23" x14ac:dyDescent="0.25">
+      <c r="Q852" s="11"/>
+      <c r="T852" s="9"/>
+      <c r="U852" s="10"/>
       <c r="V852" s="9"/>
       <c r="W852" s="10"/>
     </row>
-    <row r="853" spans="19:23" x14ac:dyDescent="0.25">
+    <row r="853" spans="17:23" x14ac:dyDescent="0.25">
       <c r="S853" s="11"/>
       <c r="V853" s="9"/>
       <c r="W853" s="10"/>
     </row>
-    <row r="854" spans="19:23" x14ac:dyDescent="0.25">
+    <row r="854" spans="17:23" x14ac:dyDescent="0.25">
       <c r="S854" s="11"/>
       <c r="V854" s="9"/>
       <c r="W854" s="10"/>
     </row>
-    <row r="855" spans="19:23" x14ac:dyDescent="0.25">
+    <row r="855" spans="17:23" x14ac:dyDescent="0.25">
       <c r="S855" s="11"/>
       <c r="V855" s="9"/>
       <c r="W855" s="10"/>
     </row>
-    <row r="856" spans="19:23" x14ac:dyDescent="0.25">
+    <row r="856" spans="17:23" x14ac:dyDescent="0.25">
       <c r="S856" s="11"/>
       <c r="V856" s="9"/>
       <c r="W856" s="10"/>
     </row>
-    <row r="857" spans="19:23" x14ac:dyDescent="0.25">
+    <row r="857" spans="17:23" x14ac:dyDescent="0.25">
       <c r="S857" s="11"/>
       <c r="V857" s="9"/>
       <c r="W857" s="10"/>
     </row>
-    <row r="858" spans="19:23" x14ac:dyDescent="0.25">
+    <row r="858" spans="17:23" x14ac:dyDescent="0.25">
       <c r="S858" s="11"/>
       <c r="V858" s="9"/>
       <c r="W858" s="10"/>
     </row>
-    <row r="859" spans="19:23" x14ac:dyDescent="0.25">
+    <row r="859" spans="17:23" x14ac:dyDescent="0.25">
       <c r="S859" s="11"/>
       <c r="V859" s="9"/>
       <c r="W859" s="10"/>
     </row>
-    <row r="860" spans="19:23" x14ac:dyDescent="0.25">
+    <row r="860" spans="17:23" x14ac:dyDescent="0.25">
       <c r="S860" s="11"/>
       <c r="V860" s="9"/>
       <c r="W860" s="10"/>
     </row>
-    <row r="861" spans="19:23" x14ac:dyDescent="0.25">
+    <row r="861" spans="17:23" x14ac:dyDescent="0.25">
       <c r="S861" s="11"/>
       <c r="V861" s="9"/>
       <c r="W861" s="10"/>
     </row>
-    <row r="862" spans="19:23" x14ac:dyDescent="0.25">
+    <row r="862" spans="17:23" x14ac:dyDescent="0.25">
       <c r="S862" s="11"/>
       <c r="V862" s="9"/>
       <c r="W862" s="10"/>
     </row>
-    <row r="863" spans="19:23" x14ac:dyDescent="0.25">
+    <row r="863" spans="17:23" x14ac:dyDescent="0.25">
       <c r="S863" s="11"/>
       <c r="V863" s="9"/>
       <c r="W863" s="10"/>
     </row>
-    <row r="864" spans="19:23" x14ac:dyDescent="0.25">
+    <row r="864" spans="17:23" x14ac:dyDescent="0.25">
       <c r="S864" s="11"/>
       <c r="V864" s="9"/>
       <c r="W864" s="10"/>
@@ -36560,6 +36809,11 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A39:A50"/>
+    <mergeCell ref="A51:A62"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="A63:A74"/>
     <mergeCell ref="S2:T2"/>
     <mergeCell ref="A3:A14"/>
     <mergeCell ref="A15:A26"/>
@@ -36570,11 +36824,6 @@
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="M2:N2"/>
-    <mergeCell ref="A39:A50"/>
-    <mergeCell ref="A51:A62"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="A63:A74"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -36582,12 +36831,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="304c15a9-2ddf-417f-8912-8cf6a1609eab">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="ec2c31f6-e4da-4ac2-b928-7a50ed07fae6" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -36846,20 +37097,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="304c15a9-2ddf-417f-8912-8cf6a1609eab">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="ec2c31f6-e4da-4ac2-b928-7a50ed07fae6" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7B921E6-00DE-4D0E-B400-431DDE188271}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11171811-4752-42CE-913B-A1196C5C2AA8}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="304c15a9-2ddf-417f-8912-8cf6a1609eab"/>
+    <ds:schemaRef ds:uri="ec2c31f6-e4da-4ac2-b928-7a50ed07fae6"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -36884,12 +37136,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{11171811-4752-42CE-913B-A1196C5C2AA8}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7B921E6-00DE-4D0E-B400-431DDE188271}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="304c15a9-2ddf-417f-8912-8cf6a1609eab"/>
-    <ds:schemaRef ds:uri="ec2c31f6-e4da-4ac2-b928-7a50ed07fae6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
